--- a/out/策略报告.xlsx
+++ b/out/策略报告.xlsx
@@ -55,7 +55,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -86,12 +86,6 @@
         <bgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -136,10 +130,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,10 +495,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
@@ -917,1156 +907,1090 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>三、推荐阅读顺序</t>
+          <t>三、分箱验证结论</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
     </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>1）先看本页的策略规则、通过规模和接纳风险；
-2）再看《2.阈值与策略》，比较保守、平衡、增长三套方案；
-3）看《3.最终分箱表现》，确认风险是否随分数单调上升；
-4）看《4.稳定性验证》，确认 OOT、PSI、AUC、KS 和跨月表现；
-5）分箱过程、数据质量和显著性检验主要用于技术复核。</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>psi_total</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0.00558287517282086</v>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>四、重要提示</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>train_1m5_monotonic</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>本报告中的保守、平衡、增长方案由 Train 风险水平和探索性约束动态生成，用于帮助比较风险与规模，不等于最终上线审批结果。上线前应替换或补充正式的风险上限、收益、EL、人工审核产能和业务风险偏好。</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>train_3m30p_monotonic</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>oot_1m5_monotonic</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>五、分箱验证结论</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>oot_3m30p_monotonic</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>train_3m30p_auc</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0.721376055418854</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>psi_total</t>
+          <t>oot_3m30p_auc</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0.00558287517282086</v>
+        <v>0.6563316627321273</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>train_1m5_monotonic</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="b">
-        <v>1</v>
+          <t>oot_3m30p_auc_drop</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0.06504439268672668</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>train_3m30p_monotonic</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="b">
-        <v>1</v>
+          <t>months_with_3m30p_violation</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>oot_1m5_monotonic</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="b">
-        <v>0</v>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>当前分箱仍需结合倒挂、漂移或成熟度问题进一步复核</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>oot_3m30p_monotonic</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="b">
-        <v>0</v>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Train/OOT 分布稳定；Train 的 MOB3 30+ 单调；OOT 的 MOB3 30+ 存在倒挂；OOT AUC 下降超过 0.05</t>
+        </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>train_3m30p_auc</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>0.721376055418854</v>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>oot_3m30p_auc</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>0.6563316627321273</v>
-      </c>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>四、样本范围与成熟度</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>oot_3m30p_auc_drop</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>0.06504439268672668</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>sample_group</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>month_min</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>month_max</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>application_id_nunique</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>score_missing_cnt</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>score_missing_rate</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>1m5p_mature</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>1m5p_bad</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>1m5p_bad_rate</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>3m30p_mature</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>3m30p_bad</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>3m30p_bad_rate</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>months_with_3m30p_violation</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>11</v>
+      <c r="A44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>oot</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>20578</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>20578</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>7640</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0.05575916230366492</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>1515</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>0.07458745874587459</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
+      <c r="A45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>当前分箱仍需结合倒挂、漂移或成熟度问题进一步复核</t>
-        </is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>399930</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>399930</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>132403</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>10534</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0.07956013081274593</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>132397</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>12293</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>0.09284953586561628</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Train/OOT 分布稳定；Train 的 MOB3 30+ 单调；OOT 的 MOB3 30+ 存在倒挂；OOT AUC 下降超过 0.05</t>
-        </is>
-      </c>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>五、核心指标怎么看</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
     </row>
-    <row r="47"/>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>六、样本范围与成熟度</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>怎么看</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>sample_group</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>month_min</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>month_max</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>application_id_nunique</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>score_missing_cnt</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>score_missing_rate</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>1m5p_mature</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>1m5p_bad</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>1m5p_bad_rate</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>3m30p_mature</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>3m30p_bad</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="inlineStr">
-        <is>
-          <t>3m30p_bad_rate</t>
+      <c r="A49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>1M5</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>MOB1 时曾达到 5+ DPD，用于观察较早期风险表现。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>oot</t>
+          <t>MOB3 30+</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>20578</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>20578</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>7640</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>426</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>0.05575916230366492</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>1515</v>
-      </c>
-      <c r="M50" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="N50" s="7" t="n">
-        <v>0.07458745874587459</v>
+          <t>MOB3 时曾达到 30+ DPD，是本报告的主要风险标的。</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>箱内风险率</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>399930</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>399930</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>132403</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>10534</v>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>0.07956013081274593</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <v>132397</v>
-      </c>
-      <c r="M51" s="4" t="n">
-        <v>12293</v>
-      </c>
-      <c r="N51" s="7" t="n">
-        <v>0.09284953586561628</v>
+          <t>当前分数箱自身的坏样本率，用于判断风险是否随分数上升。</t>
+        </is>
       </c>
     </row>
-    <row r="52"/>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>累计通过率</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>从低风险端累计接纳至当前阈值时，占全部样本的比例。</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>七、核心指标怎么看</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
+      <c r="A53" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>累计风险率</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>从低风险端累计接纳至当前阈值后的整体风险水平。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>怎么看</t>
+      <c r="A54" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>边际风险率</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>从上一个阈值放宽到当前阈值时，新增人群自身的风险。</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>1M5</t>
+          <t>Train / OOT</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>MOB1 时曾达到 5+ DPD，用于观察较早期风险表现。</t>
+          <t>Train 用于学习分箱和候选阈值；OOT 用于验证跨期稳定性。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>MOB3 30+</t>
+          <t>PSI / AUC / KS</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>MOB3 时曾达到 30+ DPD，是本报告的主要风险标的。</t>
+          <t>分别观察分布漂移和模型区分能力，不能单独替代策略审批。</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>箱内风险率</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>当前分数箱自身的坏样本率，用于判断风险是否随分数上升。</t>
-        </is>
-      </c>
-    </row>
+    <row r="57"/>
     <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>累计通过率</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>从低风险端累计接纳至当前阈值时，占全部样本的比例。</t>
-        </is>
-      </c>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>六、探索性策略约束</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>累计风险率</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>从低风险端累计接纳至当前阈值后的整体风险水平。</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>strategy_name</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>objective</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>constraint_source</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>auto_constraints_max_cum_1m5p_cnt_bad_rate</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>auto_constraints_max_cum_3m30p_cnt_bad_rate</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>auto_constraints_max_marginal_3m30p_cnt_bad_rate</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>accept_constraints_max_cum_1m5p_cnt_bad_rate</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>accept_constraints_max_cum_3m30p_cnt_bad_rate</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>accept_constraints_max_marginal_3m30p_cnt_bad_rate</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>边际风险率</t>
+          <t>保守方案</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>从上一个阈值放宽到当前阈值时，新增人群自身的风险。</t>
-        </is>
+          <t>优先控制风险，覆盖低风险核心人群</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>data_driven_exploratory</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0.05171408502828486</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.06035219831265059</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>0.1021344894521779</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>0.06364810465019675</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>0.07427962869249304</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>0.1021344894521779</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Train / OOT</t>
+          <t>平衡方案</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Train 用于学习分箱和候选阈值；OOT 用于验证跨期稳定性。</t>
-        </is>
+          <t>平衡通过规模、累计风险和边际风险</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>data_driven_exploratory</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0.06205690203394183</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.0724226379751807</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>0.1299893502118628</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>0.07796892819649101</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>0.09099254514830396</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>0.1299893502118628</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>PSI / AUC / KS</t>
+          <t>增长方案</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>分别观察分布漂移和模型区分能力，不能单独替代策略审批。</t>
-        </is>
+          <t>在总体风险附近扩大接纳规模</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>data_driven_exploratory</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0.07160411773147134</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.08356458227905465</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0.1671291645581093</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0.08910734651027545</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>0.1039914801694903</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>0.1671291645581093</v>
       </c>
     </row>
     <row r="63"/>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>八、探索性策略约束</t>
+          <t>七、运行配置</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>strategy_name</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>objective</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>constraint_source</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>auto_constraints_max_cum_1m5p_cnt_bad_rate</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>auto_constraints_max_cum_3m30p_cnt_bad_rate</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>auto_constraints_max_marginal_3m30p_cnt_bad_rate</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>accept_constraints_max_cum_1m5p_cnt_bad_rate</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>accept_constraints_max_cum_3m30p_cnt_bad_rate</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>accept_constraints_max_marginal_3m30p_cnt_bad_rate</t>
+          <t>值</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>0</v>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>data_dir</t>
+        </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>保守方案</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>优先控制风险，覆盖低风险核心人群</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>data_driven_exploratory</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>0.05171408502828486</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>0.06035219831265059</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>0.1021344894521779</v>
-      </c>
-      <c r="H66" s="7" t="n">
-        <v>0.06364810465019675</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>0.07427962869249304</v>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>0.1021344894521779</v>
+          <t>C:\Users\zhangyuliang02\Desktop\credit-model-binning\res</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>1</v>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>train_end_month</t>
+        </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>平衡方案</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>平衡通过规模、累计风险和边际风险</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>data_driven_exploratory</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>0.06205690203394183</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>0.0724226379751807</v>
-      </c>
-      <c r="G67" s="7" t="n">
-        <v>0.1299893502118628</v>
-      </c>
-      <c r="H67" s="7" t="n">
-        <v>0.07796892819649101</v>
-      </c>
-      <c r="I67" s="7" t="n">
-        <v>0.09099254514830396</v>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>0.1299893502118628</v>
+          <t>2026-03</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>2</v>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>oot_start_month</t>
+        </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>增长方案</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>在总体风险附近扩大接纳规模</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>data_driven_exploratory</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0.07160411773147134</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>0.08356458227905465</v>
-      </c>
-      <c r="G68" s="7" t="n">
-        <v>0.1671291645581093</v>
-      </c>
-      <c r="H68" s="7" t="n">
-        <v>0.08910734651027545</v>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>0.1039914801694903</v>
-      </c>
-      <c r="J68" s="7" t="n">
-        <v>0.1671291645581093</v>
+          <t>2026-04</t>
+        </is>
       </c>
     </row>
-    <row r="69"/>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>score_col</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>score_mlt</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>九、运行配置</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>score_direction</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>高分高风险</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>initial_bins_requested</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>data_dir</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>C:\Users\zhangyuliang02\Desktop\credit-model-binning\res</t>
-        </is>
+          <t>initial_bins_actual</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>train_end_month</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
+          <t>final_bins</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>oot_start_month</t>
+          <t>score_missing_decision</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>人工审核</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>score_col</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>score_mlt</t>
-        </is>
+          <t>rounded_decimals_used</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>score_direction</t>
+          <t>report_path</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>高分高风险</t>
+          <t>C:\Users\zhangyuliang02\Desktop\credit-model-binning\out\策略报告.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>initial_bins_requested</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
+    <row r="77"/>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>initial_bins_actual</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>20</v>
-      </c>
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>八、数据关键检查</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>final_bins</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n">
-        <v>8</v>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>score_missing_decision</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>人工审核</t>
-        </is>
+          <t>sample_rows_after_dedup</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
+        <v>420508</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>rounded_decimals_used</t>
+          <t>application_rows_after_dedup</t>
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>4</v>
+        <v>420508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>report_path</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>C:\Users\zhangyuliang02\Desktop\credit-model-binning\out\策略报告.xlsx</t>
-        </is>
+          <t>score_rows_after_dedup</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>420508</v>
       </c>
     </row>
-    <row r="83"/>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>analysis_rows</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>420508</v>
+      </c>
+    </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>十、数据关键检查</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>application_id_nunique</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n">
+        <v>420508</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>值</t>
-        </is>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>application_key_duplicate_cnt</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>sample_rows_after_dedup</t>
+          <t>score_missing_cnt</t>
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>420508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>application_rows_after_dedup</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>420508</v>
+          <t>score_missing_rate</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>score_rows_after_dedup</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>420508</v>
+          <t>application_month_min</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>analysis_rows</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>420508</v>
+          <t>application_month_max</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>application_id_nunique</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>420508</v>
-      </c>
-    </row>
+    <row r="90"/>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>application_key_duplicate_cnt</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>九、风险标签来源</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+      <c r="J91" s="2" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>score_missing_cnt</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>0</v>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>target_key</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>label_col</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>invalid_existing_label_cnt</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>filled_or_derived_from_dpd_cnt</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>mature_cnt</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>bad_cnt</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>missing_cnt</t>
+        </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>score_missing_rate</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>0</v>
+      <c r="A93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>1M5</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>1m5p</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>duedate_1m_5</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>existing_label_plus_dpd_fill</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>140043</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>10960</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>280465</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>application_month_min</t>
-        </is>
+      <c r="A94" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>application_month_max</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="96"/>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>十一、风险标签来源</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="2" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>target_key</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>label_col</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>invalid_existing_label_cnt</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>filled_or_derived_from_dpd_cnt</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>mature_cnt</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>bad_cnt</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>missing_cnt</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>1M5</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>1m5p</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>duedate_1m_5</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
+          <t>MOB3 30+</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>3m30p</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>duedate_3m_30</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
         <is>
           <t>existing_label_plus_dpd_fill</t>
         </is>
       </c>
-      <c r="F99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="4" t="n">
-        <v>140043</v>
-      </c>
-      <c r="I99" s="4" t="n">
-        <v>10960</v>
-      </c>
-      <c r="J99" s="4" t="n">
-        <v>280465</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>MOB3 30+</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>3m30p</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>duedate_3m_30</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>existing_label_plus_dpd_fill</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4" t="n">
+      <c r="F94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="H100" s="4" t="n">
+      <c r="H94" s="4" t="n">
         <v>133912</v>
       </c>
-      <c r="I100" s="4" t="n">
+      <c r="I94" s="4" t="n">
         <v>12406</v>
       </c>
-      <c r="J100" s="4" t="n">
+      <c r="J94" s="4" t="n">
         <v>286596</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A97:J97"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A84:B84"/>
+  <mergeCells count="9">
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A91:J91"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A42:N42"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2175,7 +2099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阅读提示</t>
+          <t>使用指引</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -33454,7 +33378,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阅读提示</t>
+          <t>使用指引</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -51069,7 +50993,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阅读提示</t>
+          <t>使用指引</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -68133,7 +68057,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阅读提示</t>
+          <t>使用指引</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>

--- a/out/策略报告.xlsx
+++ b/out/策略报告.xlsx
@@ -204,7 +204,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -581,8 +581,8 @@
   <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="89" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -6757,8 +6757,8 @@
   <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -6769,7 +6769,7 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="27" customWidth="1" min="11" max="11"/>
     <col width="31" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="57" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -9358,11 +9358,11 @@
   <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="53" customWidth="1" min="1" max="1"/>
+    <col width="91" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -9370,7 +9370,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
     <col width="36" customWidth="1" min="15" max="15"/>
     <col width="39" customWidth="1" min="16" max="16"/>
@@ -12581,7 +12581,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -12593,8 +12593,8 @@
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
